--- a/data/Antigen 2 - info sheet.xlsx
+++ b/data/Antigen 2 - info sheet.xlsx
@@ -828,7 +828,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:R168"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.35"/>
@@ -836,7 +836,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.04"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10.88"/>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B75" s="0" t="s">
         <v>19</v>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B79" s="0" t="s">
         <v>27</v>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B82" s="0" t="s">
         <v>19</v>
@@ -6058,7 +6058,7 @@
     </row>
     <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B94" s="0" t="s">
         <v>89</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B98" s="0" t="s">
         <v>27</v>
@@ -6394,7 +6394,7 @@
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B100" s="0" t="n">
         <v>1</v>
@@ -6506,7 +6506,7 @@
     </row>
     <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B102" s="0" t="s">
         <v>27</v>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B104" s="0" t="n">
         <v>1</v>
@@ -6730,7 +6730,7 @@
     </row>
     <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B106" s="0" t="s">
         <v>19</v>
@@ -6954,7 +6954,7 @@
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B110" s="0" t="s">
         <v>19</v>
@@ -7122,7 +7122,7 @@
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B113" s="0" t="s">
         <v>19</v>
@@ -7290,7 +7290,7 @@
     </row>
     <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B116" s="0" t="s">
         <v>19</v>
@@ -7402,7 +7402,7 @@
     </row>
     <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B118" s="0" t="s">
         <v>19</v>
@@ -7682,7 +7682,7 @@
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B123" s="0" t="s">
         <v>19</v>
@@ -7794,7 +7794,7 @@
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B125" s="0" t="n">
         <v>3</v>
@@ -7906,7 +7906,7 @@
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B127" s="0" t="s">
         <v>27</v>
@@ -8018,7 +8018,7 @@
     </row>
     <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B129" s="0" t="s">
         <v>83</v>
@@ -8130,7 +8130,7 @@
     </row>
     <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B131" s="0" t="n">
         <v>1</v>
@@ -8242,7 +8242,7 @@
     </row>
     <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B133" s="0" t="s">
         <v>19</v>
@@ -8410,7 +8410,7 @@
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B136" s="0" t="n">
         <v>3</v>
@@ -8522,7 +8522,7 @@
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B138" s="0" t="s">
         <v>27</v>
@@ -8634,7 +8634,7 @@
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B140" s="0" t="s">
         <v>19</v>
@@ -8802,7 +8802,7 @@
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B143" s="0" t="s">
         <v>19</v>
@@ -9026,7 +9026,7 @@
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B147" s="0" t="s">
         <v>19</v>
@@ -9194,7 +9194,7 @@
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B150" s="0" t="s">
         <v>19</v>
@@ -9362,7 +9362,7 @@
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B153" s="0" t="s">
         <v>19</v>
@@ -9530,7 +9530,7 @@
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B156" s="0" t="s">
         <v>19</v>
@@ -9642,7 +9642,7 @@
     </row>
     <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B158" s="0" t="s">
         <v>19</v>
@@ -9810,7 +9810,7 @@
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B161" s="0" t="s">
         <v>27</v>
@@ -9922,7 +9922,7 @@
     </row>
     <row r="163" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B163" s="0" t="n">
         <v>2</v>
@@ -10034,7 +10034,7 @@
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B165" s="0" t="s">
         <v>27</v>
@@ -10146,7 +10146,7 @@
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="0" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B167" s="0" t="n">
         <v>1</v>
